--- a/input/Domains/Game/TreasureTable.xlsx
+++ b/input/Domains/Game/TreasureTable.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC2C313-59A7-A748-9F03-E850289173B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49730265-DB56-3A4B-AE38-807B79642AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="1680" windowWidth="27700" windowHeight="16880" activeTab="1" xr2:uid="{01BE4A96-B5D6-5B4E-8BC6-57E1A1D6A4AB}"/>
+    <workbookView xWindow="10260" yWindow="2660" windowWidth="27700" windowHeight="16880" activeTab="1" xr2:uid="{01BE4A96-B5D6-5B4E-8BC6-57E1A1D6A4AB}"/>
   </bookViews>
   <sheets>
-    <sheet name="TREASURE_CHEST" sheetId="1" r:id="rId1"/>
-    <sheet name="TREASURE_PROGRESS" sheetId="3" r:id="rId2"/>
-    <sheet name="TREASURE_GROUP" sheetId="4" r:id="rId3"/>
-    <sheet name="REWARD@TREASURE" sheetId="2" r:id="rId4"/>
+    <sheet name="TREASURE_CHEST" sheetId="3" r:id="rId1"/>
+    <sheet name="TREASURE_REWARD" sheetId="4" r:id="rId2"/>
+    <sheet name="REWARD@TREASURE" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="45">
   <si>
     <t>rewardGroupId</t>
   </si>
@@ -125,52 +124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>treasureGroupId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>treasure_group_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>treasure_group_002</t>
-  </si>
-  <si>
-    <t>treasure_group_003</t>
-  </si>
-  <si>
-    <t>treasure_group_004</t>
-  </si>
-  <si>
-    <t>treasure_group_005</t>
-  </si>
-  <si>
-    <t>reward_treasure_group_001</t>
-  </si>
-  <si>
-    <t>reward_treasure_group_001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>reward_treasure_group_002</t>
-  </si>
-  <si>
-    <t>reward_treasure_group_003</t>
-  </si>
-  <si>
-    <t>reward_treasure_group_004</t>
-  </si>
-  <si>
-    <t>reward_treasure_group_005</t>
-  </si>
-  <si>
-    <t>TREASURE_GRADE_TYPE</t>
-  </si>
-  <si>
-    <t>TREASURE_GROUP.treasureGroupId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>maxExp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,6 +133,64 @@
   </si>
   <si>
     <t>treasureGradeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conditionMsgId</t>
+  </si>
+  <si>
+    <t>conditionOp</t>
+  </si>
+  <si>
+    <t>conditionValue</t>
+  </si>
+  <si>
+    <t>GAME_MESSAGE_OP_TYPE</t>
+  </si>
+  <si>
+    <t>class:CBigInt</t>
+  </si>
+  <si>
+    <t>NONE/EQ/GTE/LTE</t>
+  </si>
+  <si>
+    <t>조건 목표값_x000D__x000D__x000D__x000D__x000D_
+{base, pow}</t>
+  </si>
+  <si>
+    <t>TREASURE_GRADE_TYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_treasure_001_common</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_treasure_001_rare</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_treasure_001_epic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_treasure_001_legendary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_treasure_001_mythic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_stage_max</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GTE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -571,101 +582,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A055976-EA64-E443-A7BD-8E30D73BE6A8}">
-  <dimension ref="A1:B14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925D3F97-1825-DD4B-996F-ECD983C3D85A}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="C5" s="1">
         <v>20</v>
       </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="C8" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="C9" s="1">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -674,61 +687,90 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925D3F97-1825-DD4B-996F-ECD983C3D85A}">
-  <dimension ref="A1:D9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46ECA6E4-CCF8-A64F-B9B9-4FF71C8B22BB}">
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -736,13 +778,17 @@
         <v>19</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="str">
+        <f>"reward_treasure_"&amp;TEXT(C5,"000")&amp;"_"&amp;LOWER(B5)</f>
+        <v>reward_treasure_001_common</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -750,13 +796,17 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="str">
+        <f t="shared" ref="G6:G9" si="0">"reward_treasure_"&amp;TEXT(C6,"000")&amp;"_"&amp;LOWER(B6)</f>
+        <v>reward_treasure_001_rare</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -764,13 +814,17 @@
         <v>21</v>
       </c>
       <c r="C7" s="1">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>reward_treasure_001_epic</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -778,13 +832,17 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>75</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>reward_treasure_001_legendary</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -792,10 +850,134 @@
         <v>23</v>
       </c>
       <c r="C9" s="1">
-        <v>100</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>reward_treasure_001_mythic</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>"reward_treasure_"&amp;TEXT(C10,"000")&amp;"_"&amp;LOWER(B10)</f>
+        <v>reward_treasure_002_common</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="1">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f t="shared" ref="G11:G14" si="1">"reward_treasure_"&amp;TEXT(C11,"000")&amp;"_"&amp;LOWER(B11)</f>
+        <v>reward_treasure_002_rare</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>reward_treasure_002_epic</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>reward_treasure_002_legendary</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>reward_treasure_002_mythic</v>
       </c>
     </row>
   </sheetData>
@@ -805,112 +987,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46ECA6E4-CCF8-A64F-B9B9-4FF71C8B22BB}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="8.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C9A264-1B87-8846-9955-742486D0FE55}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
@@ -994,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
@@ -1014,7 +1090,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
@@ -1034,7 +1110,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
@@ -1054,7 +1130,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>17</v>
@@ -1074,7 +1150,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>

--- a/input/Domains/Game/TreasureTable.xlsx
+++ b/input/Domains/Game/TreasureTable.xlsx
@@ -475,31 +475,31 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>treasure_grade_type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>max_exp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>TREASURE_GRADE_TYPE</t>
+          <t>ITEM_GRADE_TYPE</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -509,67 +509,66 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>pk</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>COMMON</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>RARE</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>EPIC</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>LEGENDARY</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
@@ -577,7 +576,7 @@
           <t>MYTHIC</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>100</v>
       </c>
     </row>
@@ -604,98 +603,98 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>treasure_grade_type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>condition_msg_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>condition_op</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>condition_value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>reward_group_id</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>TREASURE_GRADE_TYPE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>ITEM_GRADE_TYPE</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>GAME_MESSAGE_OP_TYPE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>class:CBigInt</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>pk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>group:true</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>NONE/EQ/GTE/LTE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>조건 목표값_x000D__x000D__x000D__x000D__x000D_
 {base, pow}</t>
@@ -703,75 +702,75 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>COMMON</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="0">
         <f>"reward_treasure_"&amp;TEXT(C5,"000")&amp;"_"&amp;LOWER(B5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>RARE</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <f>"reward_treasure_"&amp;TEXT(C6,"000")&amp;"_"&amp;LOWER(B6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>EPIC</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="0">
         <f>"reward_treasure_"&amp;TEXT(C7,"000")&amp;"_"&amp;LOWER(B7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>LEGENDARY</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="0">
         <f>"reward_treasure_"&amp;TEXT(C8,"000")&amp;"_"&amp;LOWER(B8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
@@ -779,136 +778,136 @@
           <t>MYTHIC</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="0">
         <f>"reward_treasure_"&amp;TEXT(C9,"000")&amp;"_"&amp;LOWER(B9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>COMMON</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>msg_stage_max</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>GTE</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="0">
         <f>"reward_treasure_"&amp;TEXT(C10,"000")&amp;"_"&amp;LOWER(B10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>RARE</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>msg_stage_max</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>GTE</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="0">
         <f>"reward_treasure_"&amp;TEXT(C11,"000")&amp;"_"&amp;LOWER(B11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>EPIC</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>msg_stage_max</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>GTE</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="0">
         <f>"reward_treasure_"&amp;TEXT(C12,"000")&amp;"_"&amp;LOWER(B12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>LEGENDARY</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>msg_stage_max</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>GTE</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="0">
         <f>"reward_treasure_"&amp;TEXT(C13,"000")&amp;"_"&amp;LOWER(B13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
@@ -916,23 +915,23 @@
           <t>MYTHIC</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>msg_stage_max</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>GTE</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="0">
         <f>"reward_treasure_"&amp;TEXT(C14,"000")&amp;"_"&amp;LOWER(B14)</f>
         <v/>
       </c>
@@ -948,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="9.28515625" customWidth="1" style="1" min="1" max="1"/>
@@ -956,245 +955,238 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>reward_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>reward_group_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>enum:REWARD_TYPE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>pk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>group:true</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Reward PK (auto-increment number)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Reward Group Key</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>Reward Type</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>Target ID</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>reward_treasure_001_common</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>JEWEL_FREE</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>reward_treasure_001_rare</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>JEWEL_FREE</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>reward_treasure_001_epic</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>JEWEL_FREE</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>reward_treasure_001_legendary</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>JEWEL_FREE</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="0" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>reward_treasure_001_mythic</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>JEWEL_FREE</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="0" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
